--- a/sample-files/sql_usage_report2.xlsx
+++ b/sample-files/sql_usage_report2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
   <si>
     <t>Table</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Column</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>active</t>
   </si>
   <si>
@@ -58,39 +61,54 @@
     <t>sale_date</t>
   </si>
   <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>quantity_sold</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
     <t>last_sync_date</t>
   </si>
   <si>
+    <t>change_reason</t>
+  </si>
+  <si>
+    <t>logged_at</t>
+  </si>
+  <si>
+    <t>stock_after</t>
+  </si>
+  <si>
+    <t>stock_before</t>
+  </si>
+  <si>
     <t>quantity</t>
   </si>
   <si>
-    <t>product_id</t>
-  </si>
-  <si>
-    <t>id</t>
+    <t>order_id</t>
   </si>
   <si>
     <t>unit_price</t>
   </si>
   <si>
-    <t>oi</t>
-  </si>
-  <si>
-    <t>order_id</t>
+    <t>customer_name</t>
+  </si>
+  <si>
+    <t>total_amount</t>
   </si>
   <si>
     <t>order_date</t>
   </si>
   <si>
+    <t>customer_id</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
-    <t>total_amount</t>
-  </si>
-  <si>
-    <t>customer_id</t>
-  </si>
-  <si>
     <t>stock_quantity</t>
   </si>
   <si>
@@ -100,9 +118,6 @@
     <t>old_stock</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
     <t>price</t>
   </si>
   <si>
@@ -127,7 +142,7 @@
     <t>inventory_logs, products</t>
   </si>
   <si>
-    <t>inventory_logs.last_sync_date, products.category_id, products.id, products.name, products.old_stock, products.price, products.sku, products.stock_quantity, products.updated_at</t>
+    <t>inventory_logs.change_reason, inventory_logs.last_sync_date, inventory_logs.logged_at, inventory_logs.product_id, inventory_logs.stock_after, inventory_logs.stock_before, products.category_id, products.id, products.name, products.old_stock, products.price, products.sku, products.stock_quantity, products.updated_at</t>
   </si>
   <si>
     <t>etl_orders.ktr</t>
@@ -136,7 +151,7 @@
     <t>customers, order_items, order_summary, orders</t>
   </si>
   <si>
-    <t>customers.active, customers.name, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, orders.customer_id, orders.id, orders.order_date, orders.status, orders.total_amount</t>
+    <t>customers.active, customers.id, customers.name, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, order_summary.customer_name, order_summary.order_id, order_summary.total_amount, orders.customer_id, orders.id, orders.order_date, orders.status, orders.total_amount</t>
   </si>
   <si>
     <t>etl_sales.kjb</t>
@@ -145,7 +160,7 @@
     <t>daily_sales, order_items, orders, products</t>
   </si>
   <si>
-    <t>daily_sales.daily_sales, daily_sales.sale_date, order_items.id, order_items.oi, order_items.product_id, order_items.quantity, order_items.unit_price, orders.order_date, products.active, products.id, products.p</t>
+    <t>daily_sales.product_id, daily_sales.quantity_sold, daily_sales.revenue, daily_sales.sale_date, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, orders.id, orders.order_date, products.active, products.id</t>
   </si>
 </sst>
 </file>
@@ -344,11 +359,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="14.4375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.53125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -371,7 +386,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -387,10 +402,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -401,51 +416,51 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>2.0</v>
@@ -453,10 +468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>2.0</v>
@@ -464,7 +479,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -475,7 +490,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -486,73 +501,73 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
@@ -563,10 +578,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C20" t="n">
         <v>1.0</v>
@@ -574,10 +589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
         <v>1.0</v>
@@ -585,10 +600,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
         <v>1.0</v>
@@ -596,56 +611,155 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
         <v>28</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
         <v>29</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
         <v>31</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C29" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -666,46 +780,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="4">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="4">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/sample-files/sql_usage_report2.xlsx
+++ b/sample-files/sql_usage_report2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>Table</t>
   </si>
@@ -22,25 +22,25 @@
     <t>Usage Count</t>
   </si>
   <si>
-    <t>orders</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>customers</t>
-  </si>
-  <si>
-    <t>order_items</t>
-  </si>
-  <si>
-    <t>daily_sales</t>
-  </si>
-  <si>
-    <t>inventory_logs</t>
-  </si>
-  <si>
-    <t>order_summary</t>
+    <t>d_reason</t>
+  </si>
+  <si>
+    <t>f_action_audit</t>
+  </si>
+  <si>
+    <t>subscriber</t>
+  </si>
+  <si>
+    <t>f_action_detail</t>
+  </si>
+  <si>
+    <t>f_bccs_sale_sub_att</t>
+  </si>
+  <si>
+    <t>f_bccs_sale_sub_att_detail</t>
+  </si>
+  <si>
+    <t>f_sub_promotion_prepaid_pyc_1659</t>
   </si>
   <si>
     <t>Total</t>
@@ -49,82 +49,112 @@
     <t>Column</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>sale_date</t>
-  </si>
-  <si>
-    <t>product_id</t>
-  </si>
-  <si>
-    <t>quantity_sold</t>
-  </si>
-  <si>
-    <t>revenue</t>
-  </si>
-  <si>
-    <t>last_sync_date</t>
-  </si>
-  <si>
-    <t>change_reason</t>
-  </si>
-  <si>
-    <t>logged_at</t>
-  </si>
-  <si>
-    <t>stock_after</t>
-  </si>
-  <si>
-    <t>stock_before</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>order_id</t>
-  </si>
-  <si>
-    <t>unit_price</t>
-  </si>
-  <si>
-    <t>customer_name</t>
-  </si>
-  <si>
-    <t>total_amount</t>
-  </si>
-  <si>
-    <t>order_date</t>
-  </si>
-  <si>
-    <t>customer_id</t>
+    <t>b</t>
+  </si>
+  <si>
+    <t>STAFF_CODE_DKTT_KIT</t>
+  </si>
+  <si>
+    <t>sub_id</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>SHOP_CODE_DKTT_KIT</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>reason_id</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>stock_quantity</t>
-  </si>
-  <si>
-    <t>category_id</t>
-  </si>
-  <si>
-    <t>old_stock</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>updated_at</t>
+    <t>issue_datetime</t>
+  </si>
+  <si>
+    <t>partition</t>
+  </si>
+  <si>
+    <t>action_audit_id</t>
+  </si>
+  <si>
+    <t>action_code</t>
+  </si>
+  <si>
+    <t>pk_id</t>
+  </si>
+  <si>
+    <t>shop_code</t>
+  </si>
+  <si>
+    <t>issue_Datetime</t>
+  </si>
+  <si>
+    <t>pk_type</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>col_name</t>
+  </si>
+  <si>
+    <t>new_value</t>
+  </si>
+  <si>
+    <t>old_value</t>
+  </si>
+  <si>
+    <t>table_name</t>
+  </si>
+  <si>
+    <t>create_date</t>
+  </si>
+  <si>
+    <t>prepaid_amount</t>
+  </si>
+  <si>
+    <t>prepaid_code</t>
+  </si>
+  <si>
+    <t>product_code</t>
+  </si>
+  <si>
+    <t>sta_Datetime</t>
+  </si>
+  <si>
+    <t>act_status</t>
+  </si>
+  <si>
+    <t>isdn</t>
+  </si>
+  <si>
+    <t>reg_type_id</t>
+  </si>
+  <si>
+    <t>telecom_service_id</t>
+  </si>
+  <si>
+    <t>act_Status</t>
+  </si>
+  <si>
+    <t>create_user</t>
+  </si>
+  <si>
+    <t>pay_type</t>
+  </si>
+  <si>
+    <t>promotion_code</t>
+  </si>
+  <si>
+    <t>serial</t>
+  </si>
+  <si>
+    <t>sta_datetime</t>
   </si>
   <si>
     <t>File Name</t>
@@ -136,31 +166,13 @@
     <t>Columns</t>
   </si>
   <si>
-    <t>etl_inventory.ktr</t>
-  </si>
-  <si>
-    <t>inventory_logs, products</t>
-  </si>
-  <si>
-    <t>inventory_logs.change_reason, inventory_logs.last_sync_date, inventory_logs.logged_at, inventory_logs.product_id, inventory_logs.stock_after, inventory_logs.stock_before, products.category_id, products.id, products.name, products.old_stock, products.price, products.sku, products.stock_quantity, products.updated_at</t>
-  </si>
-  <si>
-    <t>etl_orders.ktr</t>
-  </si>
-  <si>
-    <t>customers, order_items, order_summary, orders</t>
-  </si>
-  <si>
-    <t>customers.active, customers.id, customers.name, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, order_summary.customer_name, order_summary.order_id, order_summary.total_amount, orders.customer_id, orders.id, orders.order_date, orders.status, orders.total_amount</t>
-  </si>
-  <si>
-    <t>etl_sales.kjb</t>
-  </si>
-  <si>
-    <t>daily_sales, order_items, orders, products</t>
-  </si>
-  <si>
-    <t>daily_sales.product_id, daily_sales.quantity_sold, daily_sales.revenue, daily_sales.sale_date, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, orders.id, orders.order_date, products.active, products.id</t>
+    <t>etl_subscriber.ktr</t>
+  </si>
+  <si>
+    <t>d_reason, f_action_audit, f_action_detail, f_bccs_sale_sub_att, f_bccs_sale_sub_att_detail, f_sub_promotion_prepaid_pyc_1659, subscriber</t>
+  </si>
+  <si>
+    <t>b.STAFF_CODE_DKTT_KIT, b.sub_id, c.SHOP_CODE_DKTT_KIT, c.sub_id, d_reason.code, d_reason.reason_id, d_reason.status, f_action_audit.action_audit_id, f_action_audit.action_code, f_action_audit.issue_Datetime, f_action_audit.issue_datetime, f_action_audit.partition, f_action_audit.pk_id, f_action_audit.pk_type, f_action_audit.reason_id, f_action_audit.shop_code, f_action_audit.user_name, f_action_detail.action_audit_id, f_action_detail.col_name, f_action_detail.issue_datetime, f_action_detail.new_value, f_action_detail.old_value, f_action_detail.partition, f_action_detail.table_name, f_sub_promotion_prepaid_pyc_1659.create_date, f_sub_promotion_prepaid_pyc_1659.partition, f_sub_promotion_prepaid_pyc_1659.prepaid_amount, f_sub_promotion_prepaid_pyc_1659.prepaid_code, f_sub_promotion_prepaid_pyc_1659.status, f_sub_promotion_prepaid_pyc_1659.sub_id, subscriber.act_Status, subscriber.act_status, subscriber.create_user, subscriber.isdn, subscriber.pay_type, subscriber.product_code, subscriber.promotion_code, subscriber.reg_type_id, subscriber.serial, subscriber.sta_Datetime, subscriber.sta_datetime, subscriber.status, subscriber.sub_id, subscriber.telecom_service_id</t>
   </si>
 </sst>
 </file>
@@ -276,7 +288,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.53125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.94140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="14.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -293,7 +305,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -301,7 +313,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -309,7 +321,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -317,7 +329,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -325,7 +337,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
@@ -333,7 +345,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -349,7 +361,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n" s="2">
-        <v>19.0</v>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
@@ -359,11 +371,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.53125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -380,21 +392,21 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -402,10 +414,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -413,43 +425,43 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>1.0</v>
@@ -457,112 +469,112 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C18" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -570,7 +582,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>2.0</v>
@@ -578,10 +590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
         <v>1.0</v>
@@ -589,10 +601,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n">
         <v>1.0</v>
@@ -600,10 +612,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
         <v>1.0</v>
@@ -611,87 +623,87 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C27" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -699,10 +711,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -710,56 +722,155 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C34" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -770,56 +881,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.16015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.4296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.98828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="50.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="4">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s" s="4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s" s="4">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/sample-files/sql_usage_report2.xlsx
+++ b/sample-files/sql_usage_report2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
   <si>
     <t>Table</t>
   </si>
@@ -22,12 +22,30 @@
     <t>Usage Count</t>
   </si>
   <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>products</t>
+  </si>
+  <si>
+    <t>customers</t>
+  </si>
+  <si>
+    <t>order_items</t>
+  </si>
+  <si>
     <t>d_reason</t>
   </si>
   <si>
+    <t>daily_sales</t>
+  </si>
+  <si>
     <t>f_action_audit</t>
   </si>
   <si>
+    <t>inventory_logs</t>
+  </si>
+  <si>
     <t>subscriber</t>
   </si>
   <si>
@@ -43,82 +61,148 @@
     <t>f_sub_promotion_prepaid_pyc_1659</t>
   </si>
   <si>
+    <t>order_summary</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>STAFF_CODE_DKTT_KIT</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>reason_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>sale_date</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>quantity_sold</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>issue_datetime</t>
+  </si>
+  <si>
+    <t>partition</t>
+  </si>
+  <si>
+    <t>action_audit_id</t>
+  </si>
+  <si>
+    <t>action_code</t>
+  </si>
+  <si>
+    <t>pk_id</t>
+  </si>
+  <si>
+    <t>shop_code</t>
+  </si>
+  <si>
+    <t>issue_Datetime</t>
+  </si>
+  <si>
+    <t>pk_type</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>col_name</t>
+  </si>
+  <si>
+    <t>new_value</t>
+  </si>
+  <si>
+    <t>old_value</t>
+  </si>
+  <si>
+    <t>table_name</t>
+  </si>
+  <si>
+    <t>create_date</t>
+  </si>
+  <si>
+    <t>prepaid_amount</t>
+  </si>
+  <si>
+    <t>prepaid_code</t>
   </si>
   <si>
     <t>sub_id</t>
   </si>
   <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>SHOP_CODE_DKTT_KIT</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>reason_id</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>issue_datetime</t>
-  </si>
-  <si>
-    <t>partition</t>
-  </si>
-  <si>
-    <t>action_audit_id</t>
-  </si>
-  <si>
-    <t>action_code</t>
-  </si>
-  <si>
-    <t>pk_id</t>
-  </si>
-  <si>
-    <t>shop_code</t>
-  </si>
-  <si>
-    <t>issue_Datetime</t>
-  </si>
-  <si>
-    <t>pk_type</t>
-  </si>
-  <si>
-    <t>user_name</t>
-  </si>
-  <si>
-    <t>col_name</t>
-  </si>
-  <si>
-    <t>new_value</t>
-  </si>
-  <si>
-    <t>old_value</t>
-  </si>
-  <si>
-    <t>table_name</t>
-  </si>
-  <si>
-    <t>create_date</t>
-  </si>
-  <si>
-    <t>prepaid_amount</t>
-  </si>
-  <si>
-    <t>prepaid_code</t>
+    <t>last_sync_date</t>
+  </si>
+  <si>
+    <t>change_reason</t>
+  </si>
+  <si>
+    <t>logged_at</t>
+  </si>
+  <si>
+    <t>stock_after</t>
+  </si>
+  <si>
+    <t>stock_before</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>unit_price</t>
+  </si>
+  <si>
+    <t>customer_name</t>
+  </si>
+  <si>
+    <t>total_amount</t>
+  </si>
+  <si>
+    <t>order_date</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>stock_quantity</t>
+  </si>
+  <si>
+    <t>category_id</t>
+  </si>
+  <si>
+    <t>old_stock</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>updated_at</t>
   </si>
   <si>
     <t>product_code</t>
@@ -166,13 +250,40 @@
     <t>Columns</t>
   </si>
   <si>
+    <t>etl_inventory.ktr</t>
+  </si>
+  <si>
+    <t>inventory_logs, products</t>
+  </si>
+  <si>
+    <t>inventory_logs.change_reason, inventory_logs.last_sync_date, inventory_logs.logged_at, inventory_logs.product_id, inventory_logs.stock_after, inventory_logs.stock_before, products.category_id, products.id, products.name, products.old_stock, products.price, products.sku, products.stock_quantity, products.updated_at</t>
+  </si>
+  <si>
+    <t>etl_orders.ktr</t>
+  </si>
+  <si>
+    <t>customers, order_items, order_summary, orders</t>
+  </si>
+  <si>
+    <t>customers.active, customers.id, customers.name, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, order_summary.customer_name, order_summary.order_id, order_summary.total_amount, orders.customer_id, orders.id, orders.order_date, orders.status, orders.total_amount</t>
+  </si>
+  <si>
+    <t>etl_sales.kjb</t>
+  </si>
+  <si>
+    <t>daily_sales, order_items, orders, products</t>
+  </si>
+  <si>
+    <t>daily_sales.product_id, daily_sales.quantity_sold, daily_sales.revenue, daily_sales.sale_date, order_items.id, order_items.order_id, order_items.product_id, order_items.quantity, order_items.unit_price, orders.id, orders.order_date, products.active, products.id</t>
+  </si>
+  <si>
     <t>etl_subscriber.ktr</t>
   </si>
   <si>
     <t>d_reason, f_action_audit, f_action_detail, f_bccs_sale_sub_att, f_bccs_sale_sub_att_detail, f_sub_promotion_prepaid_pyc_1659, subscriber</t>
   </si>
   <si>
-    <t>b.STAFF_CODE_DKTT_KIT, b.sub_id, c.SHOP_CODE_DKTT_KIT, c.sub_id, d_reason.code, d_reason.reason_id, d_reason.status, f_action_audit.action_audit_id, f_action_audit.action_code, f_action_audit.issue_Datetime, f_action_audit.issue_datetime, f_action_audit.partition, f_action_audit.pk_id, f_action_audit.pk_type, f_action_audit.reason_id, f_action_audit.shop_code, f_action_audit.user_name, f_action_detail.action_audit_id, f_action_detail.col_name, f_action_detail.issue_datetime, f_action_detail.new_value, f_action_detail.old_value, f_action_detail.partition, f_action_detail.table_name, f_sub_promotion_prepaid_pyc_1659.create_date, f_sub_promotion_prepaid_pyc_1659.partition, f_sub_promotion_prepaid_pyc_1659.prepaid_amount, f_sub_promotion_prepaid_pyc_1659.prepaid_code, f_sub_promotion_prepaid_pyc_1659.status, f_sub_promotion_prepaid_pyc_1659.sub_id, subscriber.act_Status, subscriber.act_status, subscriber.create_user, subscriber.isdn, subscriber.pay_type, subscriber.product_code, subscriber.promotion_code, subscriber.reg_type_id, subscriber.serial, subscriber.sta_Datetime, subscriber.sta_datetime, subscriber.status, subscriber.sub_id, subscriber.telecom_service_id</t>
+    <t>d_reason.code, d_reason.reason_id, d_reason.status, f_action_audit.action_audit_id, f_action_audit.action_code, f_action_audit.issue_Datetime, f_action_audit.issue_datetime, f_action_audit.partition, f_action_audit.pk_id, f_action_audit.pk_type, f_action_audit.reason_id, f_action_audit.shop_code, f_action_audit.user_name, f_action_detail.action_audit_id, f_action_detail.col_name, f_action_detail.issue_datetime, f_action_detail.new_value, f_action_detail.old_value, f_action_detail.partition, f_action_detail.table_name, f_sub_promotion_prepaid_pyc_1659.create_date, f_sub_promotion_prepaid_pyc_1659.partition, f_sub_promotion_prepaid_pyc_1659.prepaid_amount, f_sub_promotion_prepaid_pyc_1659.prepaid_code, f_sub_promotion_prepaid_pyc_1659.status, f_sub_promotion_prepaid_pyc_1659.sub_id, subscriber.act_Status, subscriber.act_status, subscriber.create_user, subscriber.isdn, subscriber.pay_type, subscriber.product_code, subscriber.promotion_code, subscriber.reg_type_id, subscriber.serial, subscriber.sta_Datetime, subscriber.sta_datetime, subscriber.status, subscriber.sub_id, subscriber.telecom_service_id</t>
   </si>
 </sst>
 </file>
@@ -285,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.94140625" customWidth="true" bestFit="true"/>
@@ -305,7 +416,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -313,7 +424,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="4">
@@ -321,7 +432,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="5">
@@ -329,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -337,7 +448,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -345,7 +456,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -353,15 +464,71 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s" s="2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="n" s="2">
-        <v>10.0</v>
+      <c r="B9" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="2">
+        <v>29.0</v>
       </c>
     </row>
   </sheetData>
@@ -371,11 +538,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.94140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.44921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="18.515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="14.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -384,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s" s="3">
         <v>1</v>
@@ -392,21 +559,21 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>1.0</v>
@@ -414,10 +581,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>1.0</v>
@@ -425,21 +592,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>2.0</v>
@@ -447,153 +614,153 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n">
         <v>1.0</v>
@@ -601,10 +768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
         <v>1.0</v>
@@ -612,21 +779,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="n">
         <v>1.0</v>
@@ -634,10 +801,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C24" t="n">
         <v>1.0</v>
@@ -645,10 +812,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C25" t="n">
         <v>1.0</v>
@@ -656,10 +823,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
         <v>1.0</v>
@@ -667,10 +834,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C27" t="n">
         <v>1.0</v>
@@ -678,10 +845,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C28" t="n">
         <v>1.0</v>
@@ -689,10 +856,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C29" t="n">
         <v>1.0</v>
@@ -700,10 +867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C30" t="n">
         <v>1.0</v>
@@ -711,10 +878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C31" t="n">
         <v>1.0</v>
@@ -722,54 +889,54 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C32" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C34" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C35" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
         <v>2.0</v>
@@ -777,43 +944,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C38" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C39" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
         <v>1.0</v>
@@ -821,56 +988,397 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C41" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C42" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C43" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C45" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" t="s">
+        <v>66</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -881,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.98828125" customWidth="true" bestFit="true"/>
@@ -891,24 +1399,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="4">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s" s="4">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s" s="4">
-        <v>49</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
